--- a/reports/latest/Test_Report.xlsx
+++ b/reports/latest/Test_Report.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 09:03:12</t>
+          <t>2026-06-22 09:03:28</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -859,7 +859,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -896,7 +896,7 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3190,7 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3597,7 +3597,7 @@
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4263,7 @@
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4485,7 +4485,7 @@
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4781,7 @@
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5077,7 @@
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5447,7 +5447,7 @@
       </c>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="G135" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5854,7 +5854,7 @@
       </c>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6002,7 @@
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6076,7 +6076,7 @@
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6520,7 @@
       </c>
       <c r="G160" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6557,7 +6557,7 @@
       </c>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="G163" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="G165" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6779,7 @@
       </c>
       <c r="G167" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="G168" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="G169" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="G170" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="G171" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="G173" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="G175" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7112,7 +7112,7 @@
       </c>
       <c r="G176" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="G177" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="G178" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="G179" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7260,7 +7260,7 @@
       </c>
       <c r="G180" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="G181" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="G182" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="G183" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="G184" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G185" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="G186" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="G187" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7556,7 @@
       </c>
       <c r="G188" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="G189" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="G190" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="G191" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="G192" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G193" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       </c>
       <c r="G194" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7815,7 +7815,7 @@
       </c>
       <c r="G195" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7852,7 +7852,7 @@
       </c>
       <c r="G196" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7889,7 +7889,7 @@
       </c>
       <c r="G197" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="G198" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="G199" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="G200" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="G201" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="G202" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="G203" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8148,7 +8148,7 @@
       </c>
       <c r="G204" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8185,7 +8185,7 @@
       </c>
       <c r="G205" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8222,7 +8222,7 @@
       </c>
       <c r="G206" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="G207" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="G208" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="G209" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="G210" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="G211" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8444,7 @@
       </c>
       <c r="G212" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8481,7 +8481,7 @@
       </c>
       <c r="G213" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="G214" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8555,7 +8555,7 @@
       </c>
       <c r="G215" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8592,7 +8592,7 @@
       </c>
       <c r="G216" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="G217" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="G218" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="G219" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="G220" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8777,7 +8777,7 @@
       </c>
       <c r="G221" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="G222" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="G223" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="G224" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="G225" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="G226" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G227" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="G228" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9073,7 +9073,7 @@
       </c>
       <c r="G229" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="G230" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="G231" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="G232" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9221,7 +9221,7 @@
       </c>
       <c r="G233" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="G234" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9295,7 +9295,7 @@
       </c>
       <c r="G235" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9332,7 +9332,7 @@
       </c>
       <c r="G236" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="G237" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="G238" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="G239" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9480,7 +9480,7 @@
       </c>
       <c r="G240" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="G241" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="G242" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="G243" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9628,7 +9628,7 @@
       </c>
       <c r="G244" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="G245" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="G246" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="G247" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="G248" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9813,7 +9813,7 @@
       </c>
       <c r="G249" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="G250" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G251" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9924,7 +9924,7 @@
       </c>
       <c r="G252" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9961,7 +9961,7 @@
       </c>
       <c r="G253" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="G254" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10035,7 +10035,7 @@
       </c>
       <c r="G255" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
       </c>
       <c r="G256" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="G257" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="G258" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10183,7 +10183,7 @@
       </c>
       <c r="G259" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10220,7 +10220,7 @@
       </c>
       <c r="G260" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10257,7 +10257,7 @@
       </c>
       <c r="G261" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="G262" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="G263" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="G264" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="G265" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10442,7 +10442,7 @@
       </c>
       <c r="G266" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="G267" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10516,7 +10516,7 @@
       </c>
       <c r="G268" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
       </c>
       <c r="G269" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="G270" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10627,7 +10627,7 @@
       </c>
       <c r="G271" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="G272" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="G273" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10738,7 +10738,7 @@
       </c>
       <c r="G274" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10775,7 +10775,7 @@
       </c>
       <c r="G275" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10812,7 +10812,7 @@
       </c>
       <c r="G276" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10849,7 +10849,7 @@
       </c>
       <c r="G277" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="G278" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="G279" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10960,7 +10960,7 @@
       </c>
       <c r="G280" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="G281" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="G282" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11071,7 +11071,7 @@
       </c>
       <c r="G283" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="G284" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11145,7 +11145,7 @@
       </c>
       <c r="G285" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11182,7 +11182,7 @@
       </c>
       <c r="G286" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11219,7 +11219,7 @@
       </c>
       <c r="G287" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11256,7 +11256,7 @@
       </c>
       <c r="G288" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="G289" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="G290" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11367,7 @@
       </c>
       <c r="G291" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11404,7 +11404,7 @@
       </c>
       <c r="G292" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11441,7 +11441,7 @@
       </c>
       <c r="G293" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="G294" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="G295" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="G296" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11589,7 +11589,7 @@
       </c>
       <c r="G297" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="G298" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11663,7 +11663,7 @@
       </c>
       <c r="G299" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11700,7 +11700,7 @@
       </c>
       <c r="G300" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11737,7 +11737,7 @@
       </c>
       <c r="G301" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11774,7 +11774,7 @@
       </c>
       <c r="G302" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11811,7 +11811,7 @@
       </c>
       <c r="G303" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11848,7 +11848,7 @@
       </c>
       <c r="G304" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="G305" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11922,7 +11922,7 @@
       </c>
       <c r="G306" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="G307" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>
@@ -11996,7 +11996,7 @@
       </c>
       <c r="G308" s="8" t="inlineStr">
         <is>
-          <t>09:03:12</t>
+          <t>09:03:28</t>
         </is>
       </c>
     </row>

--- a/reports/latest/Test_Report.xlsx
+++ b/reports/latest/Test_Report.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22 09:19:06</t>
+          <t>2026-06-22 09:19:21</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2257,7 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4033,7 @@
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4292,7 @@
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4736,7 @@
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -4995,7 +4995,7 @@
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5365,7 +5365,7 @@
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5624,7 +5624,7 @@
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="G135" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5920,7 +5920,7 @@
       </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5957,7 +5957,7 @@
       </c>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="G160" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6697,7 +6697,7 @@
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="G163" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="G165" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="G167" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="G168" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="G169" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -6993,7 +6993,7 @@
       </c>
       <c r="G170" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="G171" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
       </c>
       <c r="G173" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7178,7 @@
       </c>
       <c r="G175" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7215,7 +7215,7 @@
       </c>
       <c r="G176" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="G177" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7289,7 +7289,7 @@
       </c>
       <c r="G178" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="G179" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="G180" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="G181" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7437,7 +7437,7 @@
       </c>
       <c r="G182" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="G183" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="G184" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="G185" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="G186" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="G187" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="G188" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="G189" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7733,7 +7733,7 @@
       </c>
       <c r="G190" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7770,7 +7770,7 @@
       </c>
       <c r="G191" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="G192" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="G193" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7881,7 +7881,7 @@
       </c>
       <c r="G194" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="G195" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7955,7 +7955,7 @@
       </c>
       <c r="G196" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="G197" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="G198" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="G199" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="G200" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8140,7 +8140,7 @@
       </c>
       <c r="G201" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="G202" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8214,7 +8214,7 @@
       </c>
       <c r="G203" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="G204" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="G205" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8325,7 +8325,7 @@
       </c>
       <c r="G206" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8362,7 @@
       </c>
       <c r="G207" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="G208" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="G209" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="G210" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="G211" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8547,7 +8547,7 @@
       </c>
       <c r="G212" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8584,7 +8584,7 @@
       </c>
       <c r="G213" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8621,7 +8621,7 @@
       </c>
       <c r="G214" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="G215" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8695,7 +8695,7 @@
       </c>
       <c r="G216" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="G217" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="G218" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="G219" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8843,7 +8843,7 @@
       </c>
       <c r="G220" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="G221" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="G222" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
       </c>
       <c r="G223" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="G224" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="G225" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9065,7 +9065,7 @@
       </c>
       <c r="G226" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="G227" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="G228" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="G229" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9213,7 +9213,7 @@
       </c>
       <c r="G230" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="G231" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="G232" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9324,7 +9324,7 @@
       </c>
       <c r="G233" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9361,7 +9361,7 @@
       </c>
       <c r="G234" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="G235" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9435,7 @@
       </c>
       <c r="G236" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="G237" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="G238" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="G239" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9583,7 +9583,7 @@
       </c>
       <c r="G240" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9620,7 @@
       </c>
       <c r="G241" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9657,7 +9657,7 @@
       </c>
       <c r="G242" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="G243" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9731,7 +9731,7 @@
       </c>
       <c r="G244" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9768,7 +9768,7 @@
       </c>
       <c r="G245" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9805,7 +9805,7 @@
       </c>
       <c r="G246" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="G247" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9879,7 +9879,7 @@
       </c>
       <c r="G248" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="G249" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9953,7 +9953,7 @@
       </c>
       <c r="G250" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="G251" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="G252" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="G253" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10101,7 @@
       </c>
       <c r="G254" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10138,7 +10138,7 @@
       </c>
       <c r="G255" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="G256" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="G257" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10249,7 +10249,7 @@
       </c>
       <c r="G258" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="G259" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10323,7 +10323,7 @@
       </c>
       <c r="G260" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10360,7 +10360,7 @@
       </c>
       <c r="G261" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10397,7 +10397,7 @@
       </c>
       <c r="G262" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10434,7 @@
       </c>
       <c r="G263" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10471,7 +10471,7 @@
       </c>
       <c r="G264" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10508,7 +10508,7 @@
       </c>
       <c r="G265" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="G266" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10582,7 +10582,7 @@
       </c>
       <c r="G267" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="G268" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="G269" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10693,7 +10693,7 @@
       </c>
       <c r="G270" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10730,7 +10730,7 @@
       </c>
       <c r="G271" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10767,7 +10767,7 @@
       </c>
       <c r="G272" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="G273" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10841,7 +10841,7 @@
       </c>
       <c r="G274" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10878,7 +10878,7 @@
       </c>
       <c r="G275" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10915,7 +10915,7 @@
       </c>
       <c r="G276" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="G277" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="G278" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11026,7 +11026,7 @@
       </c>
       <c r="G279" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11063,7 +11063,7 @@
       </c>
       <c r="G280" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11100,7 +11100,7 @@
       </c>
       <c r="G281" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11137,7 +11137,7 @@
       </c>
       <c r="G282" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="G283" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="G284" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11248,7 +11248,7 @@
       </c>
       <c r="G285" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11285,7 +11285,7 @@
       </c>
       <c r="G286" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11322,7 +11322,7 @@
       </c>
       <c r="G287" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="G288" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="G289" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="G290" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11470,7 +11470,7 @@
       </c>
       <c r="G291" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11507,7 +11507,7 @@
       </c>
       <c r="G292" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11544,7 +11544,7 @@
       </c>
       <c r="G293" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11581,7 +11581,7 @@
       </c>
       <c r="G294" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11618,7 +11618,7 @@
       </c>
       <c r="G295" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="G296" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11692,7 +11692,7 @@
       </c>
       <c r="G297" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11729,7 +11729,7 @@
       </c>
       <c r="G298" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="G299" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11803,7 +11803,7 @@
       </c>
       <c r="G300" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="G301" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11877,7 +11877,7 @@
       </c>
       <c r="G302" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11914,7 +11914,7 @@
       </c>
       <c r="G303" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="G304" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -11988,7 +11988,7 @@
       </c>
       <c r="G305" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12025,7 +12025,7 @@
       </c>
       <c r="G306" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="G307" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12099,7 +12099,7 @@
       </c>
       <c r="G308" s="8" t="inlineStr">
         <is>
-          <t>09:19:06</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12196,7 +12196,7 @@
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12233,7 +12233,7 @@
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12307,7 +12307,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12344,7 +12344,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12381,7 +12381,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12455,7 +12455,7 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12751,7 +12751,7 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12788,7 +12788,7 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12825,7 +12825,7 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12862,7 +12862,7 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12899,7 +12899,7 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -12973,7 +12973,7 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13010,7 +13010,7 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13047,7 +13047,7 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13084,7 +13084,7 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13121,7 +13121,7 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13158,7 +13158,7 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13195,7 +13195,7 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13306,7 +13306,7 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13343,7 +13343,7 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13380,7 +13380,7 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13417,7 +13417,7 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13454,7 +13454,7 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13491,7 +13491,7 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13528,7 +13528,7 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13565,7 +13565,7 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13602,7 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13676,7 +13676,7 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13713,7 +13713,7 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13750,7 +13750,7 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13787,7 +13787,7 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13861,7 +13861,7 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13935,7 +13935,7 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -13972,7 +13972,7 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14046,7 +14046,7 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14083,7 +14083,7 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14120,7 +14120,7 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14157,7 +14157,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14194,7 +14194,7 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14231,7 +14231,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14268,7 +14268,7 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14305,7 +14305,7 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14379,7 +14379,7 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14416,7 +14416,7 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14453,7 +14453,7 @@
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14490,7 +14490,7 @@
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14564,7 +14564,7 @@
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14638,7 +14638,7 @@
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14675,7 +14675,7 @@
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14749,7 +14749,7 @@
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14786,7 +14786,7 @@
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14860,7 +14860,7 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14897,7 +14897,7 @@
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14934,7 +14934,7 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -14971,7 +14971,7 @@
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15008,7 +15008,7 @@
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15045,7 +15045,7 @@
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15119,7 +15119,7 @@
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15230,7 +15230,7 @@
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15267,7 +15267,7 @@
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15304,7 +15304,7 @@
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15378,7 +15378,7 @@
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15452,7 +15452,7 @@
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15489,7 +15489,7 @@
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15526,7 +15526,7 @@
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15600,7 +15600,7 @@
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15637,7 +15637,7 @@
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15674,7 +15674,7 @@
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15711,7 +15711,7 @@
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15748,7 +15748,7 @@
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15785,7 @@
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15822,7 +15822,7 @@
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15859,7 +15859,7 @@
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15896,7 +15896,7 @@
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15933,7 +15933,7 @@
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -15970,7 +15970,7 @@
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16007,7 +16007,7 @@
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16081,7 +16081,7 @@
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16155,7 +16155,7 @@
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16192,7 +16192,7 @@
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16229,7 +16229,7 @@
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16266,7 +16266,7 @@
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16340,7 +16340,7 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16377,7 +16377,7 @@
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16451,7 +16451,7 @@
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16488,7 +16488,7 @@
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16525,7 +16525,7 @@
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16562,7 +16562,7 @@
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16599,7 +16599,7 @@
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16636,7 +16636,7 @@
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16673,7 +16673,7 @@
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16821,7 +16821,7 @@
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16858,7 +16858,7 @@
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16895,7 +16895,7 @@
       </c>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16932,7 +16932,7 @@
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -16969,7 +16969,7 @@
       </c>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17043,7 +17043,7 @@
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17080,7 +17080,7 @@
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="G135" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17154,7 +17154,7 @@
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17191,7 +17191,7 @@
       </c>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17228,7 +17228,7 @@
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17265,7 +17265,7 @@
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17302,7 +17302,7 @@
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17339,7 +17339,7 @@
       </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17376,7 +17376,7 @@
       </c>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17413,7 +17413,7 @@
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17450,7 +17450,7 @@
       </c>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17487,7 +17487,7 @@
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17524,7 +17524,7 @@
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17561,7 +17561,7 @@
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17635,7 +17635,7 @@
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17709,7 +17709,7 @@
       </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17746,7 +17746,7 @@
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17783,7 +17783,7 @@
       </c>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17820,7 +17820,7 @@
       </c>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17857,7 +17857,7 @@
       </c>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17894,7 +17894,7 @@
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17931,7 +17931,7 @@
       </c>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -17968,7 +17968,7 @@
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18042,7 +18042,7 @@
       </c>
       <c r="G160" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18079,7 +18079,7 @@
       </c>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18116,7 +18116,7 @@
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18153,7 +18153,7 @@
       </c>
       <c r="G163" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18190,7 +18190,7 @@
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18227,7 +18227,7 @@
       </c>
       <c r="G165" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18264,7 +18264,7 @@
       </c>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="G167" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18338,7 +18338,7 @@
       </c>
       <c r="G168" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18375,7 +18375,7 @@
       </c>
       <c r="G169" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18412,7 +18412,7 @@
       </c>
       <c r="G170" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="G171" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18486,7 +18486,7 @@
       </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18523,7 +18523,7 @@
       </c>
       <c r="G173" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18597,7 +18597,7 @@
       </c>
       <c r="G175" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="G176" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18671,7 +18671,7 @@
       </c>
       <c r="G177" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18708,7 +18708,7 @@
       </c>
       <c r="G178" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="G179" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18782,7 +18782,7 @@
       </c>
       <c r="G180" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18819,7 +18819,7 @@
       </c>
       <c r="G181" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18856,7 +18856,7 @@
       </c>
       <c r="G182" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18893,7 +18893,7 @@
       </c>
       <c r="G183" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="G184" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -18967,7 +18967,7 @@
       </c>
       <c r="G185" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19004,7 +19004,7 @@
       </c>
       <c r="G186" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19041,7 +19041,7 @@
       </c>
       <c r="G187" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19078,7 +19078,7 @@
       </c>
       <c r="G188" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19115,7 +19115,7 @@
       </c>
       <c r="G189" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19152,7 @@
       </c>
       <c r="G190" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19189,7 +19189,7 @@
       </c>
       <c r="G191" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19226,7 +19226,7 @@
       </c>
       <c r="G192" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19263,7 +19263,7 @@
       </c>
       <c r="G193" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19300,7 +19300,7 @@
       </c>
       <c r="G194" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19337,7 +19337,7 @@
       </c>
       <c r="G195" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="G196" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19411,7 +19411,7 @@
       </c>
       <c r="G197" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19448,7 +19448,7 @@
       </c>
       <c r="G198" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19485,7 +19485,7 @@
       </c>
       <c r="G199" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19522,7 +19522,7 @@
       </c>
       <c r="G200" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="G201" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="G202" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="G203" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="G204" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19707,7 +19707,7 @@
       </c>
       <c r="G205" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19744,7 +19744,7 @@
       </c>
       <c r="G206" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19781,7 +19781,7 @@
       </c>
       <c r="G207" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19818,7 +19818,7 @@
       </c>
       <c r="G208" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19855,7 +19855,7 @@
       </c>
       <c r="G209" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19892,7 +19892,7 @@
       </c>
       <c r="G210" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19929,7 +19929,7 @@
       </c>
       <c r="G211" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -19966,7 +19966,7 @@
       </c>
       <c r="G212" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20003,7 +20003,7 @@
       </c>
       <c r="G213" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20040,7 +20040,7 @@
       </c>
       <c r="G214" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20077,7 +20077,7 @@
       </c>
       <c r="G215" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20114,7 +20114,7 @@
       </c>
       <c r="G216" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20151,7 +20151,7 @@
       </c>
       <c r="G217" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20188,7 +20188,7 @@
       </c>
       <c r="G218" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20225,7 +20225,7 @@
       </c>
       <c r="G219" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20262,7 +20262,7 @@
       </c>
       <c r="G220" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20299,7 +20299,7 @@
       </c>
       <c r="G221" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20336,7 +20336,7 @@
       </c>
       <c r="G222" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20373,7 +20373,7 @@
       </c>
       <c r="G223" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20410,7 +20410,7 @@
       </c>
       <c r="G224" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20447,7 +20447,7 @@
       </c>
       <c r="G225" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20484,7 +20484,7 @@
       </c>
       <c r="G226" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20521,7 +20521,7 @@
       </c>
       <c r="G227" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20558,7 +20558,7 @@
       </c>
       <c r="G228" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20595,7 +20595,7 @@
       </c>
       <c r="G229" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20632,7 +20632,7 @@
       </c>
       <c r="G230" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20669,7 +20669,7 @@
       </c>
       <c r="G231" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20706,7 +20706,7 @@
       </c>
       <c r="G232" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20743,7 +20743,7 @@
       </c>
       <c r="G233" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20780,7 +20780,7 @@
       </c>
       <c r="G234" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20817,7 +20817,7 @@
       </c>
       <c r="G235" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="G236" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20891,7 +20891,7 @@
       </c>
       <c r="G237" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20928,7 +20928,7 @@
       </c>
       <c r="G238" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -20965,7 +20965,7 @@
       </c>
       <c r="G239" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21002,7 +21002,7 @@
       </c>
       <c r="G240" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21039,7 +21039,7 @@
       </c>
       <c r="G241" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21076,7 +21076,7 @@
       </c>
       <c r="G242" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21113,7 +21113,7 @@
       </c>
       <c r="G243" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21150,7 +21150,7 @@
       </c>
       <c r="G244" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21187,7 +21187,7 @@
       </c>
       <c r="G245" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21224,7 +21224,7 @@
       </c>
       <c r="G246" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21261,7 +21261,7 @@
       </c>
       <c r="G247" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21298,7 +21298,7 @@
       </c>
       <c r="G248" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21335,7 +21335,7 @@
       </c>
       <c r="G249" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21372,7 +21372,7 @@
       </c>
       <c r="G250" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21409,7 +21409,7 @@
       </c>
       <c r="G251" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="G252" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21483,7 +21483,7 @@
       </c>
       <c r="G253" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21520,7 +21520,7 @@
       </c>
       <c r="G254" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21557,7 +21557,7 @@
       </c>
       <c r="G255" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="G256" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21631,7 +21631,7 @@
       </c>
       <c r="G257" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21668,7 +21668,7 @@
       </c>
       <c r="G258" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21705,7 +21705,7 @@
       </c>
       <c r="G259" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21742,7 +21742,7 @@
       </c>
       <c r="G260" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21779,7 +21779,7 @@
       </c>
       <c r="G261" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21816,7 +21816,7 @@
       </c>
       <c r="G262" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21853,7 +21853,7 @@
       </c>
       <c r="G263" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21890,7 +21890,7 @@
       </c>
       <c r="G264" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21927,7 +21927,7 @@
       </c>
       <c r="G265" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -21964,7 +21964,7 @@
       </c>
       <c r="G266" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22001,7 +22001,7 @@
       </c>
       <c r="G267" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22038,7 +22038,7 @@
       </c>
       <c r="G268" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22075,7 +22075,7 @@
       </c>
       <c r="G269" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22112,7 +22112,7 @@
       </c>
       <c r="G270" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22149,7 +22149,7 @@
       </c>
       <c r="G271" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22186,7 +22186,7 @@
       </c>
       <c r="G272" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22223,7 +22223,7 @@
       </c>
       <c r="G273" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="G274" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22297,7 +22297,7 @@
       </c>
       <c r="G275" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22334,7 +22334,7 @@
       </c>
       <c r="G276" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22371,7 +22371,7 @@
       </c>
       <c r="G277" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22408,7 +22408,7 @@
       </c>
       <c r="G278" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22445,7 +22445,7 @@
       </c>
       <c r="G279" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22482,7 +22482,7 @@
       </c>
       <c r="G280" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22519,7 +22519,7 @@
       </c>
       <c r="G281" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22556,7 +22556,7 @@
       </c>
       <c r="G282" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22593,7 +22593,7 @@
       </c>
       <c r="G283" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22630,7 +22630,7 @@
       </c>
       <c r="G284" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22667,7 +22667,7 @@
       </c>
       <c r="G285" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22704,7 +22704,7 @@
       </c>
       <c r="G286" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22741,7 +22741,7 @@
       </c>
       <c r="G287" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22778,7 +22778,7 @@
       </c>
       <c r="G288" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22815,7 +22815,7 @@
       </c>
       <c r="G289" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22852,7 +22852,7 @@
       </c>
       <c r="G290" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22889,7 +22889,7 @@
       </c>
       <c r="G291" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22926,7 +22926,7 @@
       </c>
       <c r="G292" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -22963,7 +22963,7 @@
       </c>
       <c r="G293" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23000,7 +23000,7 @@
       </c>
       <c r="G294" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23037,7 +23037,7 @@
       </c>
       <c r="G295" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23074,7 +23074,7 @@
       </c>
       <c r="G296" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23111,7 +23111,7 @@
       </c>
       <c r="G297" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23148,7 +23148,7 @@
       </c>
       <c r="G298" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23185,7 +23185,7 @@
       </c>
       <c r="G299" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23222,7 +23222,7 @@
       </c>
       <c r="G300" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23259,7 +23259,7 @@
       </c>
       <c r="G301" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23296,7 +23296,7 @@
       </c>
       <c r="G302" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23333,7 +23333,7 @@
       </c>
       <c r="G303" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23370,7 +23370,7 @@
       </c>
       <c r="G304" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23407,7 +23407,7 @@
       </c>
       <c r="G305" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23444,7 +23444,7 @@
       </c>
       <c r="G306" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23481,7 +23481,7 @@
       </c>
       <c r="G307" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23518,7 +23518,7 @@
       </c>
       <c r="G308" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23555,7 +23555,7 @@
       </c>
       <c r="G309" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23592,7 +23592,7 @@
       </c>
       <c r="G310" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23689,7 +23689,7 @@
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23726,7 +23726,7 @@
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23763,7 +23763,7 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23800,7 +23800,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23837,7 +23837,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23874,7 +23874,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23911,7 +23911,7 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23948,7 +23948,7 @@
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -23985,7 +23985,7 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24022,7 +24022,7 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24059,7 +24059,7 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24096,7 +24096,7 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24133,7 +24133,7 @@
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24170,7 +24170,7 @@
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24207,7 +24207,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24244,7 +24244,7 @@
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24281,7 +24281,7 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24318,7 +24318,7 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24355,7 +24355,7 @@
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24392,7 +24392,7 @@
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24429,7 +24429,7 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24466,7 +24466,7 @@
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24503,7 +24503,7 @@
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24540,7 +24540,7 @@
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24577,7 +24577,7 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24614,7 +24614,7 @@
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24651,7 +24651,7 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24688,7 +24688,7 @@
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24725,7 +24725,7 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24762,7 +24762,7 @@
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24799,7 +24799,7 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24836,7 +24836,7 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24873,7 +24873,7 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24910,7 +24910,7 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24947,7 +24947,7 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25021,7 +25021,7 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25058,7 +25058,7 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25095,7 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25132,7 +25132,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25169,7 +25169,7 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25206,7 +25206,7 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25243,7 +25243,7 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25280,7 +25280,7 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25317,7 +25317,7 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25354,7 +25354,7 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25391,7 +25391,7 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25428,7 +25428,7 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25465,7 +25465,7 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25502,7 +25502,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25539,7 +25539,7 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25576,7 +25576,7 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25613,7 +25613,7 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25650,7 +25650,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25687,7 +25687,7 @@
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25724,7 +25724,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25761,7 +25761,7 @@
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25835,7 +25835,7 @@
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25872,7 +25872,7 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25909,7 +25909,7 @@
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25946,7 +25946,7 @@
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -25983,7 +25983,7 @@
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26020,7 +26020,7 @@
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26057,7 +26057,7 @@
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26094,7 +26094,7 @@
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26168,7 +26168,7 @@
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26205,7 +26205,7 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26242,7 +26242,7 @@
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26279,7 +26279,7 @@
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26316,7 +26316,7 @@
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26353,7 +26353,7 @@
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26390,7 +26390,7 @@
       </c>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26464,7 +26464,7 @@
       </c>
       <c r="G77" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26501,7 +26501,7 @@
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26538,7 +26538,7 @@
       </c>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26575,7 +26575,7 @@
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26612,7 +26612,7 @@
       </c>
       <c r="G81" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26649,7 +26649,7 @@
       </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26686,7 +26686,7 @@
       </c>
       <c r="G83" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26723,7 +26723,7 @@
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26760,7 +26760,7 @@
       </c>
       <c r="G85" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26797,7 +26797,7 @@
       </c>
       <c r="G86" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="G87" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26871,7 +26871,7 @@
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26908,7 +26908,7 @@
       </c>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26945,7 +26945,7 @@
       </c>
       <c r="G90" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -26982,7 +26982,7 @@
       </c>
       <c r="G91" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27019,7 +27019,7 @@
       </c>
       <c r="G92" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27056,7 +27056,7 @@
       </c>
       <c r="G93" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27093,7 +27093,7 @@
       </c>
       <c r="G94" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27130,7 +27130,7 @@
       </c>
       <c r="G95" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27167,7 +27167,7 @@
       </c>
       <c r="G96" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27204,7 +27204,7 @@
       </c>
       <c r="G97" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27241,7 +27241,7 @@
       </c>
       <c r="G98" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27278,7 +27278,7 @@
       </c>
       <c r="G99" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27315,7 +27315,7 @@
       </c>
       <c r="G100" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27352,7 +27352,7 @@
       </c>
       <c r="G101" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27389,7 +27389,7 @@
       </c>
       <c r="G102" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27426,7 +27426,7 @@
       </c>
       <c r="G103" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27463,7 +27463,7 @@
       </c>
       <c r="G104" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27500,7 +27500,7 @@
       </c>
       <c r="G105" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27537,7 +27537,7 @@
       </c>
       <c r="G106" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27574,7 +27574,7 @@
       </c>
       <c r="G107" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27611,7 +27611,7 @@
       </c>
       <c r="G108" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27648,7 +27648,7 @@
       </c>
       <c r="G109" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27685,7 +27685,7 @@
       </c>
       <c r="G110" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27722,7 +27722,7 @@
       </c>
       <c r="G111" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27759,7 +27759,7 @@
       </c>
       <c r="G112" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27796,7 +27796,7 @@
       </c>
       <c r="G113" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27833,7 +27833,7 @@
       </c>
       <c r="G114" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27870,7 +27870,7 @@
       </c>
       <c r="G115" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27907,7 +27907,7 @@
       </c>
       <c r="G116" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27944,7 +27944,7 @@
       </c>
       <c r="G117" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -27981,7 +27981,7 @@
       </c>
       <c r="G118" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28018,7 +28018,7 @@
       </c>
       <c r="G119" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28055,7 +28055,7 @@
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28092,7 +28092,7 @@
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28129,7 +28129,7 @@
       </c>
       <c r="G122" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28166,7 +28166,7 @@
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28203,7 +28203,7 @@
       </c>
       <c r="G124" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28240,7 +28240,7 @@
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28277,7 +28277,7 @@
       </c>
       <c r="G126" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28351,7 +28351,7 @@
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28388,7 +28388,7 @@
       </c>
       <c r="G129" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28425,7 +28425,7 @@
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28462,7 +28462,7 @@
       </c>
       <c r="G131" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28499,7 +28499,7 @@
       </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28536,7 +28536,7 @@
       </c>
       <c r="G133" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28573,7 +28573,7 @@
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28610,7 +28610,7 @@
       </c>
       <c r="G135" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28647,7 +28647,7 @@
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28684,7 +28684,7 @@
       </c>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28721,7 +28721,7 @@
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28758,7 +28758,7 @@
       </c>
       <c r="G139" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28795,7 +28795,7 @@
       </c>
       <c r="G140" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28832,7 +28832,7 @@
       </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28869,7 +28869,7 @@
       </c>
       <c r="G142" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28906,7 +28906,7 @@
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28943,7 +28943,7 @@
       </c>
       <c r="G144" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -28980,7 +28980,7 @@
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29017,7 +29017,7 @@
       </c>
       <c r="G146" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29054,7 +29054,7 @@
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29091,7 +29091,7 @@
       </c>
       <c r="G148" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29128,7 +29128,7 @@
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29165,7 +29165,7 @@
       </c>
       <c r="G150" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29202,7 +29202,7 @@
       </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29239,7 +29239,7 @@
       </c>
       <c r="G152" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29276,7 +29276,7 @@
       </c>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29313,7 +29313,7 @@
       </c>
       <c r="G154" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29350,7 +29350,7 @@
       </c>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29387,7 +29387,7 @@
       </c>
       <c r="G156" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29424,7 +29424,7 @@
       </c>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29461,7 +29461,7 @@
       </c>
       <c r="G158" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29498,7 +29498,7 @@
       </c>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29535,7 +29535,7 @@
       </c>
       <c r="G160" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29572,7 +29572,7 @@
       </c>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29609,7 +29609,7 @@
       </c>
       <c r="G162" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29646,7 +29646,7 @@
       </c>
       <c r="G163" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29683,7 +29683,7 @@
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29720,7 +29720,7 @@
       </c>
       <c r="G165" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29757,7 +29757,7 @@
       </c>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29794,7 +29794,7 @@
       </c>
       <c r="G167" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29831,7 +29831,7 @@
       </c>
       <c r="G168" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29868,7 +29868,7 @@
       </c>
       <c r="G169" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29905,7 +29905,7 @@
       </c>
       <c r="G170" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29942,7 +29942,7 @@
       </c>
       <c r="G171" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -29979,7 +29979,7 @@
       </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="G173" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30053,7 +30053,7 @@
       </c>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30090,7 +30090,7 @@
       </c>
       <c r="G175" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30127,7 +30127,7 @@
       </c>
       <c r="G176" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30164,7 +30164,7 @@
       </c>
       <c r="G177" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30201,7 +30201,7 @@
       </c>
       <c r="G178" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30238,7 +30238,7 @@
       </c>
       <c r="G179" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30275,7 +30275,7 @@
       </c>
       <c r="G180" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30312,7 +30312,7 @@
       </c>
       <c r="G181" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30349,7 +30349,7 @@
       </c>
       <c r="G182" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30386,7 +30386,7 @@
       </c>
       <c r="G183" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30423,7 +30423,7 @@
       </c>
       <c r="G184" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30460,7 +30460,7 @@
       </c>
       <c r="G185" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30497,7 +30497,7 @@
       </c>
       <c r="G186" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30534,7 +30534,7 @@
       </c>
       <c r="G187" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30571,7 +30571,7 @@
       </c>
       <c r="G188" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30608,7 +30608,7 @@
       </c>
       <c r="G189" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30645,7 +30645,7 @@
       </c>
       <c r="G190" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30682,7 +30682,7 @@
       </c>
       <c r="G191" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30719,7 +30719,7 @@
       </c>
       <c r="G192" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30756,7 +30756,7 @@
       </c>
       <c r="G193" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30793,7 +30793,7 @@
       </c>
       <c r="G194" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30830,7 +30830,7 @@
       </c>
       <c r="G195" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30867,7 +30867,7 @@
       </c>
       <c r="G196" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30904,7 +30904,7 @@
       </c>
       <c r="G197" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30941,7 +30941,7 @@
       </c>
       <c r="G198" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -30978,7 +30978,7 @@
       </c>
       <c r="G199" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31015,7 +31015,7 @@
       </c>
       <c r="G200" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31052,7 +31052,7 @@
       </c>
       <c r="G201" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31089,7 +31089,7 @@
       </c>
       <c r="G202" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31126,7 +31126,7 @@
       </c>
       <c r="G203" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31163,7 +31163,7 @@
       </c>
       <c r="G204" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31200,7 +31200,7 @@
       </c>
       <c r="G205" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31237,7 +31237,7 @@
       </c>
       <c r="G206" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31274,7 +31274,7 @@
       </c>
       <c r="G207" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31311,7 +31311,7 @@
       </c>
       <c r="G208" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31348,7 +31348,7 @@
       </c>
       <c r="G209" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31385,7 +31385,7 @@
       </c>
       <c r="G210" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31422,7 +31422,7 @@
       </c>
       <c r="G211" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31459,7 +31459,7 @@
       </c>
       <c r="G212" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31496,7 +31496,7 @@
       </c>
       <c r="G213" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31533,7 +31533,7 @@
       </c>
       <c r="G214" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31570,7 +31570,7 @@
       </c>
       <c r="G215" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31607,7 +31607,7 @@
       </c>
       <c r="G216" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31644,7 +31644,7 @@
       </c>
       <c r="G217" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31681,7 +31681,7 @@
       </c>
       <c r="G218" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31718,7 +31718,7 @@
       </c>
       <c r="G219" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31755,7 +31755,7 @@
       </c>
       <c r="G220" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31792,7 +31792,7 @@
       </c>
       <c r="G221" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31829,7 +31829,7 @@
       </c>
       <c r="G222" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31866,7 +31866,7 @@
       </c>
       <c r="G223" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31903,7 +31903,7 @@
       </c>
       <c r="G224" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31940,7 +31940,7 @@
       </c>
       <c r="G225" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -31977,7 +31977,7 @@
       </c>
       <c r="G226" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32014,7 +32014,7 @@
       </c>
       <c r="G227" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32051,7 +32051,7 @@
       </c>
       <c r="G228" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32088,7 +32088,7 @@
       </c>
       <c r="G229" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32125,7 +32125,7 @@
       </c>
       <c r="G230" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32162,7 +32162,7 @@
       </c>
       <c r="G231" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32199,7 +32199,7 @@
       </c>
       <c r="G232" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32236,7 +32236,7 @@
       </c>
       <c r="G233" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="G234" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32310,7 +32310,7 @@
       </c>
       <c r="G235" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32347,7 +32347,7 @@
       </c>
       <c r="G236" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32384,7 +32384,7 @@
       </c>
       <c r="G237" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32421,7 +32421,7 @@
       </c>
       <c r="G238" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32458,7 +32458,7 @@
       </c>
       <c r="G239" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32495,7 +32495,7 @@
       </c>
       <c r="G240" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32532,7 +32532,7 @@
       </c>
       <c r="G241" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32569,7 +32569,7 @@
       </c>
       <c r="G242" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32606,7 +32606,7 @@
       </c>
       <c r="G243" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32643,7 +32643,7 @@
       </c>
       <c r="G244" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32680,7 +32680,7 @@
       </c>
       <c r="G245" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32717,7 +32717,7 @@
       </c>
       <c r="G246" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32754,7 +32754,7 @@
       </c>
       <c r="G247" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32791,7 +32791,7 @@
       </c>
       <c r="G248" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32828,7 +32828,7 @@
       </c>
       <c r="G249" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32865,7 +32865,7 @@
       </c>
       <c r="G250" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32902,7 +32902,7 @@
       </c>
       <c r="G251" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32939,7 +32939,7 @@
       </c>
       <c r="G252" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -32976,7 +32976,7 @@
       </c>
       <c r="G253" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33013,7 +33013,7 @@
       </c>
       <c r="G254" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33050,7 +33050,7 @@
       </c>
       <c r="G255" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33087,7 +33087,7 @@
       </c>
       <c r="G256" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33124,7 +33124,7 @@
       </c>
       <c r="G257" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33161,7 +33161,7 @@
       </c>
       <c r="G258" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33198,7 +33198,7 @@
       </c>
       <c r="G259" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33235,7 +33235,7 @@
       </c>
       <c r="G260" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33272,7 +33272,7 @@
       </c>
       <c r="G261" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33309,7 +33309,7 @@
       </c>
       <c r="G262" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33346,7 +33346,7 @@
       </c>
       <c r="G263" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33383,7 +33383,7 @@
       </c>
       <c r="G264" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33420,7 +33420,7 @@
       </c>
       <c r="G265" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33457,7 +33457,7 @@
       </c>
       <c r="G266" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="G267" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33531,7 +33531,7 @@
       </c>
       <c r="G268" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33568,7 +33568,7 @@
       </c>
       <c r="G269" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33605,7 +33605,7 @@
       </c>
       <c r="G270" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33642,7 +33642,7 @@
       </c>
       <c r="G271" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33679,7 +33679,7 @@
       </c>
       <c r="G272" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33716,7 +33716,7 @@
       </c>
       <c r="G273" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33753,7 +33753,7 @@
       </c>
       <c r="G274" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33790,7 +33790,7 @@
       </c>
       <c r="G275" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33827,7 +33827,7 @@
       </c>
       <c r="G276" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33864,7 +33864,7 @@
       </c>
       <c r="G277" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33901,7 +33901,7 @@
       </c>
       <c r="G278" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33938,7 +33938,7 @@
       </c>
       <c r="G279" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -33975,7 +33975,7 @@
       </c>
       <c r="G280" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34012,7 +34012,7 @@
       </c>
       <c r="G281" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34049,7 +34049,7 @@
       </c>
       <c r="G282" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34086,7 +34086,7 @@
       </c>
       <c r="G283" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34123,7 +34123,7 @@
       </c>
       <c r="G284" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34160,7 +34160,7 @@
       </c>
       <c r="G285" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34197,7 +34197,7 @@
       </c>
       <c r="G286" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34234,7 +34234,7 @@
       </c>
       <c r="G287" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34271,7 +34271,7 @@
       </c>
       <c r="G288" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34308,7 +34308,7 @@
       </c>
       <c r="G289" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34345,7 +34345,7 @@
       </c>
       <c r="G290" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34382,7 +34382,7 @@
       </c>
       <c r="G291" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34419,7 +34419,7 @@
       </c>
       <c r="G292" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34456,7 +34456,7 @@
       </c>
       <c r="G293" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34493,7 +34493,7 @@
       </c>
       <c r="G294" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34530,7 +34530,7 @@
       </c>
       <c r="G295" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34567,7 +34567,7 @@
       </c>
       <c r="G296" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34604,7 +34604,7 @@
       </c>
       <c r="G297" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34641,7 +34641,7 @@
       </c>
       <c r="G298" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34678,7 +34678,7 @@
       </c>
       <c r="G299" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34715,7 +34715,7 @@
       </c>
       <c r="G300" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34752,7 +34752,7 @@
       </c>
       <c r="G301" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34789,7 +34789,7 @@
       </c>
       <c r="G302" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34826,7 +34826,7 @@
       </c>
       <c r="G303" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34863,7 +34863,7 @@
       </c>
       <c r="G304" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34900,7 +34900,7 @@
       </c>
       <c r="G305" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
@@ -34937,7 +34937,7 @@
       </c>
       <c r="G306" s="8" t="inlineStr">
         <is>
-          <t>09:19:07</t>
+          <t>09:19:21</t>
         </is>
       </c>
     </row>
